--- a/QCM2_2_PHY.xlsx
+++ b/QCM2_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B214FBD3-0BBA-438D-B161-868674DB340C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F773AF-415E-4B01-8571-6481A79B7200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="363">
   <si>
     <t>Question</t>
   </si>
@@ -63,24 +63,9 @@
     <t>OptionE</t>
   </si>
   <si>
-    <t>À déterminer</t>
-  </si>
-  <si>
     <t>Autre réponse</t>
   </si>
   <si>
-    <t>Option D</t>
-  </si>
-  <si>
-    <t>Option B</t>
-  </si>
-  <si>
-    <t>Option A</t>
-  </si>
-  <si>
-    <t>Option C</t>
-  </si>
-  <si>
     <t>Toutes les propositions sont fausses.</t>
   </si>
   <si>
@@ -123,15 +108,9 @@
     <t>La réaction nucléaire produisant ${}_{3}^{7}Li$ à partir de ${}_{4}^{7}Be$ est du type $\beta^+$.</t>
   </si>
   <si>
-    <t>La réaction nucléaire produisant ${}_{5}^{10}X$ à partir de ${}_{4}^{10}Be$ est du type $\beta^+$.</t>
-  </si>
-  <si>
     <t>Un neutron et ${}_{6}^{12}C$</t>
   </si>
   <si>
-    <t>Un neutron et ${}_{4}^{12}Be$</t>
-  </si>
-  <si>
     <t>Un neutron et ${}_{5}^{10}X$</t>
   </si>
   <si>
@@ -213,9 +192,6 @@
     <t>$t = \tau \ln\left(\frac{N}{N_0}\right)$</t>
   </si>
   <si>
-    <t>Option A / B</t>
-  </si>
-  <si>
     <t>$t = \tau \cdot \ln(0,75)$</t>
   </si>
   <si>
@@ -349,9 +325,6 @@
   </si>
   <si>
     <t>$5$</t>
-  </si>
-  <si>
-    <t>$10^{10}$</t>
   </si>
   <si>
     <t>$22,5\text{ Bq}$</t>
@@ -1129,13 +1102,40 @@
   </si>
   <si>
     <t>L'énergie $E'$ libérée par la réaction est :</t>
+  </si>
+  <si>
+    <t>Réponse A et B</t>
+  </si>
+  <si>
+    <t>$2\alpha$ et $2\beta^-$</t>
+  </si>
+  <si>
+    <t>La réaction nucléaire produisant ${}_{5}^{10}X$ à partir de ${}_{4}^{10}Be$ est du type $\beta^-$.</t>
+  </si>
+  <si>
+    <t>Un neutron et ${}_{4}^{8}Be$</t>
+  </si>
+  <si>
+    <t>$10^{5}$</t>
+  </si>
+  <si>
+    <t>$10^{6}$</t>
+  </si>
+  <si>
+    <t>$10^{7}$</t>
+  </si>
+  <si>
+    <t>$10^{8}$</t>
+  </si>
+  <si>
+    <t>$0$</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1156,12 +1156,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Consolas"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
       <name val="Consolas"/>
     </font>
     <font>
@@ -1273,7 +1267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
@@ -1294,29 +1288,23 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1668,84 +1656,84 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="I2" s="15" t="s">
-        <v>14</v>
+      <c r="I2" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="7" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H3" s="7"/>
-      <c r="I3" s="13" t="s">
-        <v>16</v>
+      <c r="I3" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="J3" s="6"/>
       <c r="K3" s="5"/>
     </row>
     <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>13</v>
+        <v>355</v>
       </c>
       <c r="H4" s="9"/>
-      <c r="I4" s="15" t="s">
-        <v>15</v>
+      <c r="I4" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="5"/>
@@ -1753,26 +1741,26 @@
     <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>32</v>
+        <v>356</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H5" s="7"/>
-      <c r="I5" s="13" t="s">
-        <v>15</v>
+      <c r="I5" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="J5" s="4"/>
       <c r="K5" s="5"/>
@@ -1780,26 +1768,26 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>34</v>
+        <v>357</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H6" s="7"/>
-      <c r="I6" s="13" t="s">
-        <v>16</v>
+      <c r="I6" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="5"/>
@@ -1807,55 +1795,55 @@
     <row r="7" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="7" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H7" s="7"/>
-      <c r="I7" s="13" t="s">
-        <v>12</v>
+      <c r="I7" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H8" s="9"/>
-      <c r="I8" s="15" t="s">
-        <v>16</v>
+      <c r="I8" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="5"/>
@@ -1863,26 +1851,26 @@
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="7" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H9" s="7"/>
-      <c r="I9" s="13" t="s">
-        <v>15</v>
+      <c r="I9" s="7" t="s">
+        <v>37</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1890,26 +1878,26 @@
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="7" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="H10" s="7"/>
-      <c r="I10" s="13" t="s">
-        <v>15</v>
+      <c r="I10" s="7" t="s">
+        <v>40</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1917,28 +1905,28 @@
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="7" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>15</v>
+        <v>47</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1946,26 +1934,26 @@
     <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="7" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H12" s="7"/>
-      <c r="I12" s="13" t="s">
-        <v>17</v>
+      <c r="I12" s="7" t="s">
+        <v>50</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1973,26 +1961,28 @@
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="7" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="13" t="s">
-        <v>62</v>
+        <v>54</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -2000,55 +1990,55 @@
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H14" s="7"/>
-      <c r="I14" s="13" t="s">
-        <v>17</v>
+      <c r="I14" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:11" ht="153" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H15" s="9"/>
-      <c r="I15" s="15" t="s">
-        <v>15</v>
+      <c r="I15" s="9" t="s">
+        <v>59</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -2056,26 +2046,26 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="H16" s="7"/>
-      <c r="I16" s="13" t="s">
-        <v>12</v>
+      <c r="I16" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2083,26 +2073,26 @@
     <row r="17" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="7" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H17" s="7"/>
-      <c r="I17" s="13" t="s">
-        <v>17</v>
+      <c r="I17" s="7" t="s">
+        <v>68</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2110,1414 +2100,1414 @@
     <row r="18" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H18" s="7"/>
-      <c r="I18" s="13" t="s">
-        <v>12</v>
+      <c r="I18" s="7" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="H19" s="7"/>
-      <c r="I19" s="13" t="s">
-        <v>12</v>
+      <c r="I19" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H20" s="9"/>
-      <c r="I20" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>295</v>
+      <c r="I20" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="J20" s="13" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H21" s="7"/>
-      <c r="I21" s="13" t="s">
-        <v>15</v>
+      <c r="I21" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="7" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H22" s="7"/>
-      <c r="I22" s="13" t="s">
-        <v>15</v>
+      <c r="I22" s="7" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H23" s="7"/>
-      <c r="I23" s="13" t="s">
-        <v>15</v>
+      <c r="I23" s="7" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="7" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="H24" s="7"/>
-      <c r="I24" s="13" t="s">
-        <v>12</v>
+      <c r="I24" s="7" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D25" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>108</v>
+      <c r="D25" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="H25" s="9"/>
-      <c r="I25" s="15" t="s">
-        <v>12</v>
+      <c r="I25" s="7" t="s">
+        <v>360</v>
       </c>
       <c r="J25" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>108</v>
+        <v>362</v>
       </c>
       <c r="H26" s="7"/>
-      <c r="I26" s="13" t="s">
-        <v>12</v>
+      <c r="I26" s="7" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="7" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="H27" s="7"/>
-      <c r="I27" s="13" t="s">
-        <v>12</v>
+      <c r="I27" s="7" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="7" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H28" s="7"/>
-      <c r="I28" s="13" t="s">
-        <v>12</v>
+      <c r="I28" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="7" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H29" s="7"/>
-      <c r="I29" s="13" t="s">
-        <v>12</v>
+      <c r="I29" s="7" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="H30" s="9"/>
-      <c r="I30" s="15" t="s">
-        <v>15</v>
+      <c r="I30" s="9" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="7" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="H31" s="7"/>
-      <c r="I31" s="13" t="s">
-        <v>16</v>
+      <c r="I31" s="7" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="7" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H32" s="7"/>
-      <c r="I32" s="13" t="s">
-        <v>12</v>
+      <c r="I32" s="7" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="7" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H33" s="7"/>
-      <c r="I33" s="13" t="s">
-        <v>17</v>
+      <c r="I33" s="7" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="7" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H34" s="7"/>
-      <c r="I34" s="13" t="s">
-        <v>14</v>
+      <c r="I34" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="H35" s="9"/>
-      <c r="I35" s="15" t="s">
-        <v>15</v>
+      <c r="I35" s="9" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="7" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="H36" s="7"/>
-      <c r="I36" s="13" t="s">
-        <v>17</v>
+      <c r="I36" s="7" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="7" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="H37" s="7"/>
-      <c r="I37" s="13" t="s">
-        <v>16</v>
+      <c r="I37" s="7" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="7" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H38" s="7"/>
-      <c r="I38" s="13" t="s">
-        <v>16</v>
+      <c r="I38" s="7" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="7" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H39" s="7"/>
-      <c r="I39" s="13" t="s">
-        <v>17</v>
+      <c r="I39" s="7" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H40" s="9"/>
-      <c r="I40" s="15" t="s">
-        <v>14</v>
+      <c r="I40" s="9" t="s">
+        <v>149</v>
       </c>
       <c r="J40" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="7" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="H41" s="7"/>
-      <c r="I41" s="13" t="s">
-        <v>16</v>
+      <c r="I41" s="7" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="7" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>160</v>
+        <v>151</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="H42" s="7"/>
-      <c r="I42" s="13" t="s">
-        <v>12</v>
+      <c r="I42" s="7" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="7" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="H43" s="7"/>
-      <c r="I43" s="13" t="s">
-        <v>12</v>
+      <c r="I43" s="7" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="H44" s="9"/>
-      <c r="I44" s="15" t="s">
-        <v>15</v>
+      <c r="I44" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="7" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="H45" s="7"/>
-      <c r="I45" s="13" t="s">
-        <v>15</v>
+      <c r="I45" s="7" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="7" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="H46" s="7"/>
-      <c r="I46" s="13" t="s">
-        <v>15</v>
+      <c r="I46" s="7" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9"/>
-      <c r="I47" s="15" t="s">
-        <v>12</v>
+      <c r="I47" s="9" t="s">
+        <v>172</v>
       </c>
       <c r="J47" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="7" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="H48" s="7"/>
-      <c r="I48" s="13" t="s">
-        <v>15</v>
+      <c r="I48" s="7" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="7" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="H49" s="7"/>
-      <c r="I49" s="13" t="s">
-        <v>12</v>
+      <c r="I49" s="7" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="7" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="H50" s="7"/>
-      <c r="I50" s="13" t="s">
-        <v>16</v>
+      <c r="I50" s="7" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="7" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="H51" s="7"/>
-      <c r="I51" s="13" t="s">
-        <v>17</v>
+      <c r="I51" s="7" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H52" s="9"/>
-      <c r="I52" s="15" t="s">
-        <v>14</v>
+      <c r="I52" s="9" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="7" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H53" s="7"/>
-      <c r="I53" s="13" t="s">
-        <v>17</v>
+      <c r="I53" s="7" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="7" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H54" s="7"/>
-      <c r="I54" s="13" t="s">
-        <v>14</v>
+      <c r="I54" s="7" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="7" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H55" s="7"/>
-      <c r="I55" s="13" t="s">
-        <v>17</v>
+      <c r="I55" s="7" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="7" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="H56" s="7"/>
-      <c r="I56" s="13" t="s">
-        <v>12</v>
+      <c r="I56" s="7" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H57" s="9"/>
-      <c r="I57" s="15" t="s">
-        <v>17</v>
+      <c r="I57" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="7" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H58" s="7"/>
-      <c r="I58" s="13" t="s">
-        <v>15</v>
+      <c r="I58" s="7" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="7" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H59" s="7"/>
-      <c r="I59" s="13" t="s">
-        <v>16</v>
+      <c r="I59" s="7" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="7" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="H60" s="7"/>
-      <c r="I60" s="13" t="s">
-        <v>15</v>
+      <c r="I60" s="7" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="7" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E61" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>228</v>
-      </c>
       <c r="G61" s="7" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="H61" s="7"/>
-      <c r="I61" s="13" t="s">
-        <v>16</v>
+      <c r="I61" s="7" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="7" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="H62" s="7"/>
-      <c r="I62" s="13" t="s">
-        <v>17</v>
+      <c r="I62" s="7" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="7" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="H63" s="7"/>
-      <c r="I63" s="13" t="s">
-        <v>14</v>
+      <c r="I63" s="7" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="H64" s="9"/>
-      <c r="I64" s="15" t="s">
-        <v>17</v>
+      <c r="I64" s="9" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="7" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H65" s="7"/>
-      <c r="I65" s="13" t="s">
-        <v>14</v>
+      <c r="I65" s="7" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A66" s="8"/>
       <c r="B66" s="9" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="H66" s="9"/>
-      <c r="I66" s="15" t="s">
-        <v>17</v>
+      <c r="I66" s="9" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="7" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="H67" s="7"/>
-      <c r="I67" s="13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I67" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
       <c r="B68" s="7" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="H68" s="7"/>
-      <c r="I68" s="13" t="s">
-        <v>17</v>
+      <c r="I68" s="7" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
       <c r="B69" s="7" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="H69" s="7"/>
-      <c r="I69" s="13" t="s">
-        <v>15</v>
+      <c r="I69" s="7" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="I70" s="15" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="I70" s="9" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="B71" s="7" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="H71" s="7"/>
-      <c r="I71" s="13" t="s">
-        <v>17</v>
+      <c r="I71" s="7" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="H72" s="9"/>
-      <c r="I72" s="15" t="s">
-        <v>12</v>
+      <c r="I72" s="9" t="s">
+        <v>262</v>
       </c>
     </row>
   </sheetData>

--- a/QCM2_2_PHY.xlsx
+++ b/QCM2_2_PHY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MOULAY\Desktop\WEB_TEST_APP\MED-CONTEST\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F773AF-415E-4B01-8571-6481A79B7200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64372005-38CF-4DD6-93E8-F26457AFFCE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="369">
   <si>
     <t>Question</t>
   </si>
@@ -135,12 +135,6 @@
     <t>$N(t) = e^{-\lambda t}$</t>
   </si>
   <si>
-    <t>$N_0 = N(t_{1/2})$</t>
-  </si>
-  <si>
-    <t>$t_{1/2} = \frac{\ln(2)}{\lambda}$</t>
-  </si>
-  <si>
     <t>$N_0 = 2 \cdot N(t_{1/2})$</t>
   </si>
   <si>
@@ -183,15 +177,9 @@
     <t>$t = \frac{1}{\lambda} \ln\left(\frac{N_0}{N}\right)$</t>
   </si>
   <si>
-    <t>$t = \tau \ln\left(\frac{N_0}{N}\right)$</t>
-  </si>
-  <si>
     <t>$t = \frac{1}{\lambda} \ln\left(\frac{N}{N_0}\right)$</t>
   </si>
   <si>
-    <t>$t = \tau \ln\left(\frac{N}{N_0}\right)$</t>
-  </si>
-  <si>
     <t>$t = \tau \cdot \ln(0,75)$</t>
   </si>
   <si>
@@ -264,9 +252,6 @@
     <t>$\frac{\tau}{\ln(2)}$</t>
   </si>
   <si>
-    <t>$\tau$</t>
-  </si>
-  <si>
     <t>$\frac{\ln(2)}{\tau}$</t>
   </si>
   <si>
@@ -288,12 +273,6 @@
     <t>$\lambda \cdot N_0 \cdot e^{-\lambda t_1}$</t>
   </si>
   <si>
-    <t>$\lambda \cdot N_0 \cdot e^{-t_1}$</t>
-  </si>
-  <si>
-    <t>$\lambda \cdot (N_1 + N_0)$</t>
-  </si>
-  <si>
     <t>La constante de temps $\tau$ différente.</t>
   </si>
   <si>
@@ -453,18 +432,6 @@
     <t>$E_0 = 3710\text{ MeV}$</t>
   </si>
   <si>
-    <t>$N_A \cdot E_0$</t>
-  </si>
-  <si>
-    <t>$E_{TEP}$</t>
-  </si>
-  <si>
-    <t>$E_0$</t>
-  </si>
-  <si>
-    <t>$\frac{E_0}{E_{TEP}}$</t>
-  </si>
-  <si>
     <t>fission.</t>
   </si>
   <si>
@@ -480,27 +447,15 @@
     <t>$1,28 \cdot 10^{-14}\text{ J}$</t>
   </si>
   <si>
-    <t>$-2,4 \cdot 10^{-11}\text{ J}$</t>
-  </si>
-  <si>
     <t>$2,4 \cdot 10^{-9}\text{ J}$</t>
   </si>
   <si>
     <t>$2,4 \cdot 10^{-10}\text{ J}$</t>
   </si>
   <si>
-    <t>$0,142 \cdot 10^{-20}\text{ kg}$</t>
-  </si>
-  <si>
     <t>$2,7 \cdot 10^{-27}\text{ kg}$</t>
   </si>
   <si>
-    <t>$1,42 \cdot 10^{-10}\text{ kg}$</t>
-  </si>
-  <si>
-    <t>$2,7 \cdot 10^{-29}\text{ kg}$</t>
-  </si>
-  <si>
     <t>$Z + Z' = 0$</t>
   </si>
   <si>
@@ -531,12 +486,6 @@
     <t>$x = \frac{M' - M_0}{M' - M}$</t>
   </si>
   <si>
-    <t>$x = \frac{M - M_0}{M' - M}$</t>
-  </si>
-  <si>
-    <t>$x = \frac{M' - M}{M' - M}$</t>
-  </si>
-  <si>
     <t>$2000\text{ ans}$</t>
   </si>
   <si>
@@ -549,18 +498,9 @@
     <t>$8000\text{ ans}$</t>
   </si>
   <si>
-    <t>120 désinté par minute.</t>
-  </si>
-  <si>
     <t>240 désinté par minute.</t>
   </si>
   <si>
-    <t>480 désinté par minute.</t>
-  </si>
-  <si>
-    <t>960 désinté par minute.</t>
-  </si>
-  <si>
     <t>2 fois moins de désintégrations qu'aujourd'hui.</t>
   </si>
   <si>
@@ -609,12 +549,6 @@
     <t>$6,9 \cdot 10^{13}\text{ J par kg d'uranium 235}$</t>
   </si>
   <si>
-    <t>$\Delta m = 14,3\text{ u}$</t>
-  </si>
-  <si>
-    <t>$\Delta m = 17,9\text{ u}$</t>
-  </si>
-  <si>
     <t>$\Delta m = 1,43\text{ u}$</t>
   </si>
   <si>
@@ -711,18 +645,9 @@
     <t>La masse ne se conserve pas</t>
   </si>
   <si>
-    <t>$Z = 39, N = 19$</t>
-  </si>
-  <si>
     <t>$Z = 19, N = 40$</t>
   </si>
   <si>
-    <t>$Z = 19, N = 21$</t>
-  </si>
-  <si>
-    <t>$Z = 40, N = 19$</t>
-  </si>
-  <si>
     <t>isomères</t>
   </si>
   <si>
@@ -753,12 +678,6 @@
     <t>$N_0 = N_A - N_K$</t>
   </si>
   <si>
-    <t>$\frac{N_A + N_K}{N_0} = 1$</t>
-  </si>
-  <si>
-    <t>$\frac{N_A + N_K}{N_0} = 0$</t>
-  </si>
-  <si>
     <t>$t_1 = 3,9 \cdot 10^9\text{ ans}$</t>
   </si>
   <si>
@@ -832,9 +751,6 @@
   </si>
   <si>
     <t>On considère l'équation suivante : ${}_{86}^{222}Rn$ aboutit au ${}_{82}^{206}Pb$ par émissions de :</t>
-  </si>
-  <si>
-    <t>On donne : ${}_{4}^{7}Be$, ${}_{3}^{7}Li$, ${}_{6}^{12}C$, ${}_{5}^{10}X$.</t>
   </si>
   <si>
     <t>Un atome de ${}_{4}^{9}Be$ fixe une particule alpha pour libérer :</t>
@@ -868,10 +784,6 @@
     <t>Au bout d'un temps t inconnu, on observe que la population a diminué de 25 % par rapport à t=0. On a la relation :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Datation :&lt;/b&gt;&lt;/center&gt; 
-Pour dater un morceau de bois ancien, on utilise la méthode de datation au carbone 14, dont le temps de demi-vie est de l'ordre de 5600 ans. Dans cet échantillon de bois ancien, on mesure en moyenne 10 désintégrations par minute et par gramme de carbone. On estime que chaque gramme de carbone d'un organisme vivant contient $7 \cdot 10^{10}$ atomes de carbone 14. On donne: $365 \times 24 = 8760$ et $365 \times 24 \times 3600 = 3,15 \cdot 10^7$ ; $\ln(2) = 0,7$ ; $\ln(3) = 1,1$ ; $\ln(7) = 1,9$ ; $\ln(10) = 2,3$.</t>
-  </si>
-  <si>
     <t>Le nombre de noyaux qui contient encore cet échantillon est :</t>
   </si>
   <si>
@@ -931,10 +843,6 @@
     <t>L'activité de l'élément X dans l'organisme de Samir le 31 mai 2020 juste après 12 h est voisine de celle :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;Noyau-masse-énergie : &lt;/b&gt;&lt;/center&gt;
-On considère la réaction A et la réaction B : A : ${}_{1}^{2}H + {}_{1}^{3}H \rightarrow {}_{2}^{4}He + {}_{0}^{1}n$ | B : ${}_{1}^{2}H + {}_{1}^{2}H \rightarrow {}_{2}^{3}He + {}_{0}^{1}n$. On donne: $m({}_{1}^{2}H)=2,013\text{ u}$; $m({}_{1}^{3}H)=3,015\text{ u}$; $m({}_{0}^{1}n)=1,009\text{ u}$; $m({}_{2}^{4}He)=4,001\text{ u}$; $1\text{ u} \approx 1,66 \cdot 10^{-27}\text{ kg}$; $1\text{ eV} = 1,6 \cdot 10^{-19}\text{ J}$; $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
     <t>Les deux réactions sont :</t>
   </si>
   <si>
@@ -950,10 +858,6 @@
     <t>Les deux réactions ont :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;La réaction nucléaire : &lt;/b&gt;&lt;/center&gt;
-On considère la réaction nucléaire suivante: ${}_{92}^{235}U + {}_{0}^{1}n \rightarrow {}_{38}^{94}Sr + {}_{54}^{140}Xe + z {}_{0}^{1}n$. x, y et z sont des entiers et n représente un neutron. On donne les énergies de liaison (MeV) des noyaux: ${}_{92}^{235}U: 1760$ ; ${}_{38}^{94}Sr: 800$ ; ${}_{54}^{140}Xe: 1150$. On note $m_U$ la masse du noyau d'uranium ; $N_A$ Le nombre d'Avogadro ; $E_{TEP}$ L'énergie libérée par 1 T.E.P (tonne équivalent pétrole).</t>
-  </si>
-  <si>
     <t>z est égale :</t>
   </si>
   <si>
@@ -972,20 +876,10 @@
     <t>PHY_QCM2_1_Q3.png</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;La courbe d'Aston : &lt;/b&gt;&lt;/center&gt;
-On considère la courbe d'Aston suivante. On donne : la charge élémentaire vaut $1,6 \cdot 10^{-19}\text{ C}$. La célérité de la lumière vaut $3 \cdot 10^8\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
     <t>$X_1$ peut évoluer en $X_2$ par :</t>
   </si>
   <si>
     <t>$X_4$ peut évoluer en $X_3$ par :</t>
-  </si>
-  <si>
-    <t>L'énergie de liaison de $X_1$ est :</t>
-  </si>
-  <si>
-    <t>Le défaut de masse de $X_1$ est :</t>
   </si>
   <si>
     <t>&lt;center&gt;&lt;b&gt;Deux Isotopes : &lt;/b&gt;&lt;/center&gt;
@@ -1008,9 +902,6 @@
     <t>Le temps de demi-vie du carbone 14 est :</t>
   </si>
   <si>
-    <t>Pour le bois récent on mesure $A\text{ (Bq)}$ :</t>
-  </si>
-  <si>
     <t>Le bois ancien date d'environ :</t>
   </si>
   <si>
@@ -1035,23 +926,12 @@
     <t>400 TEP fournissent autant d'énergie que :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;La réaction de fission : &lt;/b&gt;&lt;/center&gt;
-On considère la réaction de fission suivante : ${}_{92}^{235}U + {}_{0}^{1}n \rightarrow {}_{58}^{146}Ce + {}_{34}^{85}Se + 5 {}_{0}^{1}n$. On donne : $m({}_{92}^{235}U) = 234,993\text{ u}$; $m({}_{58}^{146}Ce) = 145,878\text{ u}$; $m({}_{34}^{85}Se) = 84,903\text{ u}$; $m({}_{0}^{1}n) = 1,008\text{ u}$; $m({}_{1}^{1}p) = 1,007\text{ u}$; $1\text{ u} = 1,66 \cdot 10^{-27}\text{ kg}$; $1\text{ eV} = 1,6 \cdot 10^{-19}\text{ J}$; $N_A = 6,02 \cdot 10^{23}\text{ mol}^{-1}$; $1\text{ TEP} = 40,5 \cdot 10^9\text{ J}$; $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;L'iode 131 : &lt;/b&gt;&lt;/center&gt;
-L'iode 131 ${}_{53}^{131}I$ se désintègre en Xénon ${}_{54}^{131}Xe$. On donne : la demi-vie de ${}_{53}^{131}I$ est $t_{1/2} = 8\text{ jours}$ ; $\ln 5 = 1,6$ ; $\ln 2 = 0,7$.</t>
-  </si>
-  <si>
     <t>Cette désintégration est de type :</t>
   </si>
   <si>
     <t>L'instant où 75% des noyaux se désintègrent :</t>
   </si>
   <si>
-    <t>L'instant où 2/8 des noyaux se désintègrent :</t>
-  </si>
-  <si>
     <t>L'instant où 99% des noyaux se désintègrent :</t>
   </si>
   <si>
@@ -1062,13 +942,6 @@
   </si>
   <si>
     <t>Pendant une réaction nucléaire :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Roches volcaniques : &lt;/b&gt;&lt;/center&gt;
-Certaines roches volcaniques contiennent du potassium (symbole K) dont une partie est l'isotope 40 (Z=19; A=40) qui se désintègre en calcium ${}^{40}Ca$ et en un gaz inerte l'argon ${}^{40}Ar$ (Z=18). La demi-vie du potassium 40 étant $1,3 \cdot 10^9\text{ ans}$, la datation sera basée sur la proportion, dans la roche, du potassium et de l'argon. Cette méthode permet de dater l'ensemble des $4,6 \cdot 10^9\text{ ans}$ d'histoire de la terre.</t>
-  </si>
-  <si>
-    <t>La composition de noyau du potassium ${}_{19}^{40}K$ est :</t>
   </si>
   <si>
     <t>Les deux noyaux ${}_{19}^{39}K$ et ${}_{19}^{40}K$ sont des :</t>
@@ -1078,41 +951,21 @@
 &lt;br&gt;&lt;br&gt;L'équation correspondante (on supposera pour simplifier que cette équation ne fait intervenir qu'un neutron, un proton et un électron) :</t>
   </si>
   <si>
-    <t>En notant $\lambda$ la constante de radioactivité du potassium 40, $N_K$ le nombre d'atomes de potassium 40 et $N_A$ le nombre d'atomes d'argon 40 présents à une date t dans un échantillon contenant initialement $N_0$ atomes de potassium 40 uniquement. La relation entre $N_K$, $N_A$ et $N_0$ est :</t>
-  </si>
-  <si>
     <t>L'instant $t_1$ où $N_A = N_K$ est :</t>
   </si>
   <si>
-    <t>Pour dater la formation de cette roche, un géologue analyse un échantillon d'obsidienne et constate que les atomes d'argon y sont 3 fois plus nombreux que les atomes de potassium 40. L'âge de cette roche est :</t>
-  </si>
-  <si>
-    <t>&lt;center&gt;&lt;b&gt;Un échantillon de xénon : &lt;/b&gt;&lt;/center&gt;
-Le xénon ${}_{54}^{131}Xe$ est radioactif $\beta^-$, le noyau fils est ${}_{Z}^{A}Cs$. On considère à la date $t_0 = 0$, un échantillon de xénon de masse $m_0$ et d'activité radioactive $a_0$. Son activité à la date $t_1 = 19,25\text{ h}$ est $a_1 = 142\text{ Bq}$. On donne : $\lambda = 2 \cdot 10^{-5}\text{ s}^{-1}$ ; $e^{1,386} \approx 4$ ; $19,25 \times 3600 = 69300$.</t>
-  </si>
-  <si>
     <t>Choisir la proposition juste :</t>
   </si>
   <si>
     <t>La valeur de l'activité $a_0$ est :</t>
   </si>
   <si>
-    <t>&lt;center&gt;&lt;b&gt;L'hydrogène : &lt;/b&gt;&lt;/center&gt;
-La transformation de $1\text{ g}$ d'hydrogène en hélium 4 selon la réaction : $4 {}_{1}^{1}H \rightarrow {}_{2}^{4}He + 2 {}_{1}^{0}e$ s'accompagne de la libération d'une énergie est égale à $4,1 \cdot 10^{32}\text{ eV}$. On donne : $N_A = 6,02 \cdot 10^{23}\text{ mol}^{-1}$.</t>
-  </si>
-  <si>
     <t>L'énergie $E'$ libérée par la réaction est :</t>
   </si>
   <si>
-    <t>Réponse A et B</t>
-  </si>
-  <si>
     <t>$2\alpha$ et $2\beta^-$</t>
   </si>
   <si>
-    <t>La réaction nucléaire produisant ${}_{5}^{10}X$ à partir de ${}_{4}^{10}Be$ est du type $\beta^-$.</t>
-  </si>
-  <si>
     <t>Un neutron et ${}_{4}^{8}Be$</t>
   </si>
   <si>
@@ -1129,6 +982,189 @@
   </si>
   <si>
     <t>$0$</t>
+  </si>
+  <si>
+    <t>On donne : ${}_{4}^{10}Be$,${}_{4}^{9}Be$,${}_{4}^{8}Be$,${}_{4}^{7}Be$, ${}_{3}^{7}Li$, ${}_{6}^{12}C$, ${}_{5}^{10}X$.</t>
+  </si>
+  <si>
+    <t>La réaction nucléaire produisant ${}_{5}^{10}X$ à partir de ${}_{4}^{10}Be$ est du type $\beta^+$.</t>
+  </si>
+  <si>
+    <t>$t_{1/2} = {\ln(2)} \cdot {\lambda}$</t>
+  </si>
+  <si>
+    <t>$t_{1/2} = \frac{2}{\lambda}$</t>
+  </si>
+  <si>
+    <t>$N_0 = \frac{N(t_{1/2})}{2}$</t>
+  </si>
+  <si>
+    <t>Divisé par $\ln(16)$</t>
+  </si>
+  <si>
+    <t>$t = \cdot {\lambda} \ln\left(\frac{N_0}{N}\right)$</t>
+  </si>
+  <si>
+    <t>$t = \frac{1}{\lambda} \ln\left(\frac{N_0}{2}\right)$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Datation :&lt;/b&gt;&lt;/center&gt; 
+Pour dater un morceau de bois ancien, on utilise la méthode de datation au carbone 14, dont le temps de demi-vie est de l'ordre de 5600 ans. Dans cet échantillon de bois ancien, on mesure en moyenne 10 désintégrations par minute et par gramme de carbone. On estime que chaque gramme de carbone d'un organisme vivant contient $7 \cdot 10^{10}$ atomes de carbone 14. 
+&lt;br&gt;On donne: $365 \times 24 = 8760$ et $365 \times 24 \times 3600 = 3,15 \cdot 10^7$ ; $\ln(2) = 0,7$ ; $\ln(3) = 1,1$ ; $\ln(7) = 1,9$ ; $\ln(10) = 2,3$.</t>
+  </si>
+  <si>
+    <t>$4,2 \cdot 10^{11}$</t>
+  </si>
+  <si>
+    <t>$\frac{\tau}{2}$</t>
+  </si>
+  <si>
+    <t>$\frac{N_0 + N_1}{t_1}$</t>
+  </si>
+  <si>
+    <t>$a_0 \cdot e^{-\lambda t}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Noyau-masse-énergie : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On considère la réaction A et la réaction B : 
+&lt;br&gt;A : ${}_{1}^{2}H + {}_{1}^{3}H \rightarrow {}_{2}^{4}He + {}_{0}^{1}n$ 
+&lt;br&gt; B : ${}_{1}^{2}H + {}_{1}^{2}H \rightarrow {}_{2}^{3}He + {}_{0}^{1}n$. 
+&lt;br&gt;On donne: $m({}_{1}^{1}H)=1,011\text{ u}$;$m({}_{1}^{2}H)=2,013\text{ u}$; $m({}_{1}^{3}H)=3,015\text{ u}$; $m({}_{0}^{1}n)=1,009\text{ u}$; $m({}_{2}^{4}He)=4,001\text{ u}$; $1\text{ u}= \frac{5}{3} \cdot 10^{-27}\text{ kg}$; $1\text{ eV} = \frac{5}{3} \cdot 10^{-19}\text{ J}$; $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La réaction nucléaire : &lt;/b&gt;&lt;/center&gt;
+On considère la réaction nucléaire suivante: 
+&lt;br&gt;${}_{92}^{235}U + {}_{x}^{y}p \rightarrow {}_{38}^{94}Sr + {}_{54}^{140}Xe + z {}_{x}^{y}p$. 
+x, y et z sont des entiers et n représente un neutron. 
+On donne les énergies de liaison (MeV) des noyaux: ${}_{92}^{235}U: 1760$ ; $\quad$ ${}_{38}^{94}Sr: 800$ ; $\quad$ ${}_{54}^{140}Xe: 1150$. 
+On note $m_U$ la masse du noyau d'uranium ; $N_A$ Le nombre d'Avogadro ; 
+$E_{TEP}$ L'énergie libérée par 1 T.E.P (tonne équivalent pétrole).</t>
+  </si>
+  <si>
+    <t>$E = N_A \cdot E_0$</t>
+  </si>
+  <si>
+    <t>$E = E_0$</t>
+  </si>
+  <si>
+    <t>$E = \frac{E_0}{N_A}$</t>
+  </si>
+  <si>
+    <t>$E = \frac{N_A}{E_0}$</t>
+  </si>
+  <si>
+    <t>$\frac{E_0}{m_U \cdot E_{TEP}}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La courbe d'Aston : &lt;/b&gt;&lt;/center&gt;
+On considère la courbe d'Aston suivante. 
+On donne : 
+la charge élémentaire vaut $1,6 \cdot 10^{-19}\text{ C}$. 
+La célérité de la lumière vaut $3 \cdot 10^8\text{ m.s}^{-1}$.</t>
+  </si>
+  <si>
+    <t>L'énergie de liaison de $X_3$ est :</t>
+  </si>
+  <si>
+    <t>$2,4 \cdot 10^{-11}\text{ J}$</t>
+  </si>
+  <si>
+    <t>Le défaut de masse de $X_3$ est :</t>
+  </si>
+  <si>
+    <t>$0,142 \cdot 10^{-30}\text{ kg}$</t>
+  </si>
+  <si>
+    <t>$1,42 \cdot 10^{-30}\text{ kg}$</t>
+  </si>
+  <si>
+    <t>$2,7 \cdot 10^{-26}\text{ kg}$</t>
+  </si>
+  <si>
+    <t>$x = \frac{M' - M}{M_0 - M}$</t>
+  </si>
+  <si>
+    <t>$x = \frac{M_0 - M}{M' - M}$</t>
+  </si>
+  <si>
+    <t>Pour le bois récent on mesure :</t>
+  </si>
+  <si>
+    <t>120 désintégrations par minute.</t>
+  </si>
+  <si>
+    <t>240 désintégrations par minute.</t>
+  </si>
+  <si>
+    <t>480 désintégrations par minute.</t>
+  </si>
+  <si>
+    <t>960 désintégrations par minute.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;La réaction de fission : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+On considère la réaction de fission suivante : 
+&lt;br&gt;${}_{92}^{235}U + {}_{0}^{1}n \rightarrow {}_{58}^{146}Ce + {}_{34}^{85}Se + 5 {}_{0}^{1}n$. 
+&lt;br&gt;On donne : $m({}_{92}^{235}U) = 234,993\text{ u}$; $m({}_{58}^{146}Ce) = 145,878\text{ u}$; $m({}_{34}^{85}Se) = 84,903\text{ u}$; $m({}_{0}^{1}n) = 1,008\text{ u}$; $m({}_{1}^{1}p) = 1,007\text{ u}$; 
+$1\text{ u} = \frac{5}{3} \cdot 10^{-27}\text{ kg}$; $1\text{ eV} =  \frac{5}{3} \cdot 10^{-19}\text{ J}$; $N_A = 6,02 \cdot 10^{23}\text{ mol}^{-1}$; $1\text{ TEP} = 40,5 \cdot 10^9\text{ J}$; $c = 3 \cdot 10^8\text{ m.s}^{-1}$.</t>
+  </si>
+  <si>
+    <t>$\Delta m = 143\text{ u}$</t>
+  </si>
+  <si>
+    <t>$\Delta m = 179\text{ u}$</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;L'iode 131 : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+L'iode 131 ${}_{53}^{131}I$ se désintègre en Xénon ${}_{54}^{131}Xe$. 
+On donne : la demi-vie de ${}_{53}^{131}I$ est $t_{1/2} = 8\text{ jours}$ ; $\ln 5 = 1,6$ ; $\ln 2 = 0,7$.</t>
+  </si>
+  <si>
+    <t>L'instant où 7/8 des noyaux se désintègrent :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Roches volcaniques : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Certaines roches volcaniques contiennent du potassium (symbole K) dont une partie est l'isotope 40 (Z=19; A=40) qui se désintègre en calcium ${}^{40}Ca$ et en un gaz inerte l'argon ${}^{40}Ar$ (Z=18). La demi-vie du potassium 40 étant $1,3 \cdot 10^9\text{ ans}$, la datation sera basée sur la proportion, dans la roche, du potassium et de l'argon. Cette méthode permet de dater l'ensemble des $4,6 \cdot 10^9\text{ ans}$ d'histoire de la terre.</t>
+  </si>
+  <si>
+    <t>La composition de noyau du potassium ${}_{19}^{39}K$ est :</t>
+  </si>
+  <si>
+    <t>$Z = 19, \quad N = 39$</t>
+  </si>
+  <si>
+    <t>$Z = 19, N = 20$</t>
+  </si>
+  <si>
+    <t>$Z = 19, N = 18$</t>
+  </si>
+  <si>
+    <t>En notant $\lambda$ la constante de radioactivité du potassium 40, $N_K$ le nombre d'atomes de potassium 40 et $N_A$ le nombre d'atomes d'argon 40 présents à une date t dans un échantillon contenant initialement $N_0$ atomes de potassium 40 uniquement. 
+La relation entre $N_K$, $N_A$ et $N_0$ est :</t>
+  </si>
+  <si>
+    <t>$\frac{N_A}{N_0} + \frac{N_K}{N_0}= 1$</t>
+  </si>
+  <si>
+    <t>$\frac{N_A}{N_0} + \frac{N_K}{N_0}= 0$</t>
+  </si>
+  <si>
+    <t>Pour dater la formation de cette roche, un géologue analyse un échantillon d'obsidienne et constate que les atomes d'argon y sont 3 fois plus nombreux que les atomes de potassium 40. 
+L'âge de cette roche est :</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;Un échantillon de xénon : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;Le xénon ${}_{54}^{131}Xe$ est radioactif $\beta^-$, le noyau fils est ${}_{Z}^{A}Cs$. On considère à la date $t_0 = 0$, un échantillon de xénon de masse $m_0$ et d'activité radioactive $a_0$. Son activité à la date $t_1 = 19,25\text{ h}$ est $a_1 = 142\text{ Bq}$. On donne : $\lambda = 2 \cdot 10^{-5}\text{ s}^{-1}$ ; $e^{1,386} \approx 4$ ; $19,25 \times 36 = 693$.</t>
+  </si>
+  <si>
+    <t>&lt;center&gt;&lt;b&gt;L'hydrogène : &lt;/b&gt;&lt;/center&gt;&lt;br&gt;
+&lt;br&gt;La transformation de $1\text{ g}$ d'hydrogène en hélium 4 selon la réaction : $4 {}_{1}^{1}H \rightarrow {}_{2}^{4}He + 2 {}_{1}^{0}e$ s'accompagne de la libération d'une énergie est égale à $4,1 \cdot 10^{32}\text{ eV}$. On donne : $N_A = 6,02 \cdot 10^{23}\text{ mol}^{-1}$.</t>
+  </si>
+  <si>
+    <t>$\frac{E_{TEP}}{m_U \cdot E_{0}}$</t>
+  </si>
+  <si>
+    <t>$\frac{E_{TEP}}{m_U}$</t>
   </si>
 </sst>
 </file>
@@ -1656,10 +1692,10 @@
     </row>
     <row r="2" spans="1:11" ht="181.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="C2" s="10" t="s">
         <v>3</v>
@@ -1685,7 +1721,7 @@
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="11"/>
       <c r="B3" s="7" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="C3" s="12" t="s">
         <v>3</v>
@@ -1711,10 +1747,10 @@
     </row>
     <row r="4" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>268</v>
+        <v>241</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>3</v>
@@ -1729,7 +1765,7 @@
         <v>24</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>355</v>
+        <v>310</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
@@ -1741,7 +1777,7 @@
     <row r="5" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A5" s="11"/>
       <c r="B5" s="7" t="s">
-        <v>269</v>
+        <v>317</v>
       </c>
       <c r="C5" s="12" t="s">
         <v>3</v>
@@ -1753,7 +1789,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>356</v>
+        <v>318</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>17</v>
@@ -1768,7 +1804,7 @@
     <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="11"/>
       <c r="B6" s="7" t="s">
-        <v>270</v>
+        <v>242</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>3</v>
@@ -1777,7 +1813,7 @@
         <v>27</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>357</v>
+        <v>311</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>28</v>
@@ -1795,7 +1831,7 @@
     <row r="7" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A7" s="11"/>
       <c r="B7" s="7" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>3</v>
@@ -1821,10 +1857,10 @@
     </row>
     <row r="8" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>3</v>
@@ -1851,26 +1887,26 @@
     <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="11"/>
       <c r="B9" s="7" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="G9" s="7" t="s">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="H9" s="7"/>
       <c r="I9" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1878,26 +1914,26 @@
     <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A10" s="11"/>
       <c r="B10" s="7" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="G10" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="H10" s="7"/>
       <c r="I10" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1905,28 +1941,28 @@
     <row r="11" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="11"/>
       <c r="B11" s="7" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="F11" s="7" t="s">
+      <c r="H11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>47</v>
-      </c>
       <c r="I11" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1934,26 +1970,26 @@
     <row r="12" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A12" s="11"/>
       <c r="B12" s="7" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="C12" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="G12" s="7" t="s">
-        <v>17</v>
+        <v>322</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1961,28 +1997,26 @@
     <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A13" s="11"/>
       <c r="B13" s="7" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>51</v>
+        <v>323</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>354</v>
-      </c>
+        <v>324</v>
+      </c>
+      <c r="H13" s="7"/>
       <c r="I13" s="7" t="s">
-        <v>354</v>
+        <v>49</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1990,55 +2024,55 @@
     <row r="14" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11"/>
       <c r="B14" s="7" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H14" s="7"/>
       <c r="I14" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:11" ht="153" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>280</v>
+        <v>325</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>59</v>
+        <v>326</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" s="9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -2046,26 +2080,26 @@
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="11"/>
       <c r="B16" s="7" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H16" s="7"/>
       <c r="I16" s="7" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -2073,26 +2107,26 @@
     <row r="17" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11"/>
       <c r="B17" s="7" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="7"/>
       <c r="I17" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -2100,431 +2134,430 @@
     <row r="18" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11"/>
       <c r="B18" s="7" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H18" s="7"/>
       <c r="I18" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="11"/>
       <c r="B19" s="7" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H19" s="7"/>
       <c r="I19" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H20" s="9"/>
       <c r="I20" s="9" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11"/>
       <c r="B21" s="7" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="C21" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="7"/>
+        <v>77</v>
+      </c>
       <c r="I21" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11"/>
       <c r="B22" s="7" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="C22" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>86</v>
+        <v>329</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>88</v>
+        <v>328</v>
       </c>
       <c r="H22" s="7"/>
       <c r="I22" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
       <c r="B23" s="7" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="C23" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H23" s="7"/>
       <c r="I23" s="7" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11"/>
       <c r="B24" s="7" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="H24" s="7"/>
       <c r="I24" s="7" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="114.75" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>358</v>
+        <v>312</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>359</v>
+        <v>313</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>361</v>
+        <v>315</v>
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="7" t="s">
-        <v>360</v>
+        <v>314</v>
       </c>
       <c r="J25" t="s">
-        <v>292</v>
+        <v>263</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A26" s="11"/>
       <c r="B26" s="7" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="C26" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>362</v>
+        <v>316</v>
       </c>
       <c r="H26" s="7"/>
       <c r="I26" s="7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="11"/>
       <c r="B27" s="7" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="C27" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="11"/>
       <c r="B28" s="7" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="C28" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="H28" s="7"/>
       <c r="I28" s="7" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11"/>
       <c r="B29" s="7" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="C29" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H29" s="7"/>
       <c r="I29" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" ht="165.75" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="178.5" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>300</v>
+        <v>330</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H30" s="9"/>
       <c r="I30" s="9" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
       <c r="B31" s="7" t="s">
-        <v>302</v>
+        <v>272</v>
       </c>
       <c r="C31" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="H31" s="7"/>
       <c r="I31" s="7" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="11"/>
       <c r="B32" s="7" t="s">
-        <v>303</v>
+        <v>273</v>
       </c>
       <c r="C32" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="H32" s="7"/>
       <c r="I32" s="7" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="11"/>
       <c r="B33" s="7" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="C33" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="H33" s="7"/>
       <c r="I33" s="7" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="11"/>
       <c r="B34" s="7" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="C34" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>17</v>
@@ -2534,980 +2567,980 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="140.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" ht="165.75" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>307</v>
+        <v>276</v>
       </c>
       <c r="C35" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="9" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11"/>
       <c r="B36" s="7" t="s">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="H36" s="7"/>
       <c r="I36" s="7" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A37" s="11"/>
       <c r="B37" s="7" t="s">
-        <v>309</v>
+        <v>278</v>
       </c>
       <c r="C37" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="H37" s="7"/>
       <c r="I37" s="7" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11"/>
       <c r="B38" s="7" t="s">
-        <v>310</v>
+        <v>279</v>
       </c>
       <c r="C38" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>142</v>
+        <v>334</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>143</v>
+        <v>335</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>12</v>
+        <v>332</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>12</v>
+        <v>333</v>
       </c>
       <c r="H38" s="7"/>
       <c r="I38" s="7" t="s">
-        <v>142</v>
+        <v>332</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A39" s="11"/>
       <c r="B39" s="7" t="s">
-        <v>311</v>
+        <v>280</v>
       </c>
       <c r="C39" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>144</v>
+        <v>336</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>143</v>
+        <v>367</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>145</v>
+        <v>368</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>17</v>
       </c>
       <c r="H39" s="7"/>
       <c r="I39" s="7" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>313</v>
+        <v>337</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>314</v>
+        <v>282</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H40" s="9"/>
       <c r="I40" s="9" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="J40" t="s">
-        <v>312</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="11"/>
       <c r="B41" s="7" t="s">
-        <v>315</v>
+        <v>283</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="H41" s="7"/>
       <c r="I41" s="7" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="11"/>
       <c r="B42" s="7" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>151</v>
+        <v>339</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="H42" s="7"/>
       <c r="I42" s="7" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11"/>
       <c r="B43" s="7" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C43" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>154</v>
+        <v>341</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>156</v>
+        <v>342</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>157</v>
+        <v>343</v>
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="7" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>318</v>
+        <v>284</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="H44" s="9"/>
       <c r="I44" s="9" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="11"/>
       <c r="B45" s="7" t="s">
-        <v>319</v>
+        <v>285</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="H45" s="7"/>
       <c r="I45" s="7" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="11"/>
       <c r="B46" s="7" t="s">
-        <v>320</v>
+        <v>286</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>167</v>
+        <v>344</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>168</v>
+        <v>345</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="H46" s="7"/>
       <c r="I46" s="7" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>321</v>
+        <v>287</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>323</v>
+        <v>289</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="9" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="J47" t="s">
-        <v>322</v>
+        <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="11"/>
       <c r="B48" s="7" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="C48" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>174</v>
+        <v>347</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>175</v>
+        <v>348</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>176</v>
+        <v>349</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>177</v>
+        <v>350</v>
       </c>
       <c r="H48" s="7"/>
       <c r="I48" s="7" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="11"/>
       <c r="B49" s="7" t="s">
-        <v>325</v>
+        <v>290</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="H49" s="7"/>
       <c r="I49" s="7" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A50" s="11"/>
       <c r="B50" s="7" t="s">
-        <v>326</v>
+        <v>291</v>
       </c>
       <c r="C50" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="H50" s="7"/>
       <c r="I50" s="7" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A51" s="11"/>
       <c r="B51" s="7" t="s">
-        <v>327</v>
+        <v>292</v>
       </c>
       <c r="C51" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="H51" s="7"/>
       <c r="I51" s="7" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" ht="165.75" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="191.25" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>328</v>
+        <v>293</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="G52" s="9" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="H52" s="9"/>
       <c r="I52" s="9" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A53" s="11"/>
       <c r="B53" s="7" t="s">
-        <v>329</v>
+        <v>294</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>190</v>
+        <v>171</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>191</v>
+        <v>170</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="H53" s="7"/>
       <c r="I53" s="7" t="s">
-        <v>192</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="11"/>
       <c r="B54" s="7" t="s">
-        <v>330</v>
+        <v>295</v>
       </c>
       <c r="C54" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>194</v>
+        <v>352</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>195</v>
+        <v>353</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="H54" s="7"/>
       <c r="I54" s="7" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="11"/>
       <c r="B55" s="7" t="s">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="F55" s="7" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="H55" s="7"/>
       <c r="I55" s="7" t="s">
-        <v>199</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="11"/>
       <c r="B56" s="7" t="s">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="H56" s="7"/>
       <c r="I56" s="7" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>335</v>
+        <v>298</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G57" s="9" t="s">
         <v>12</v>
       </c>
       <c r="H57" s="9"/>
       <c r="I57" s="9" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="11"/>
       <c r="B58" s="7" t="s">
-        <v>336</v>
+        <v>299</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H58" s="7"/>
       <c r="I58" s="7" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="11"/>
       <c r="B59" s="7" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C59" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="H59" s="7"/>
       <c r="I59" s="7" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="11"/>
       <c r="B60" s="7" t="s">
-        <v>338</v>
+        <v>300</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="H60" s="7"/>
       <c r="I60" s="7" t="s">
-        <v>215</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="11"/>
       <c r="B61" s="7" t="s">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="C61" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="H61" s="7"/>
       <c r="I61" s="7" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A62" s="11"/>
       <c r="B62" s="7" t="s">
-        <v>340</v>
+        <v>302</v>
       </c>
       <c r="C62" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="H62" s="7"/>
       <c r="I62" s="7" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A63" s="11"/>
       <c r="B63" s="7" t="s">
-        <v>341</v>
+        <v>303</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="H63" s="7"/>
       <c r="I63" s="7" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="140.25" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>228</v>
+        <v>358</v>
       </c>
       <c r="E64" s="9" t="s">
-        <v>229</v>
+        <v>359</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="H64" s="9"/>
       <c r="I64" s="9" t="s">
-        <v>230</v>
+        <v>359</v>
       </c>
     </row>
     <row r="65" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A65" s="11"/>
       <c r="B65" s="7" t="s">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>232</v>
+        <v>207</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
       <c r="H65" s="7"/>
       <c r="I65" s="7" t="s">
-        <v>235</v>
+        <v>210</v>
       </c>
     </row>
     <row r="66" spans="1:9" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A66" s="8"/>
       <c r="B66" s="9" t="s">
-        <v>345</v>
+        <v>305</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>236</v>
+        <v>211</v>
       </c>
       <c r="E66" s="9" t="s">
-        <v>237</v>
+        <v>212</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="H66" s="9"/>
       <c r="I66" s="9" t="s">
-        <v>238</v>
+        <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A67" s="11"/>
       <c r="B67" s="7" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="C67" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>240</v>
+        <v>215</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>242</v>
+        <v>362</v>
       </c>
       <c r="G67" s="7" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="H67" s="7"/>
       <c r="I67" s="7" t="s">
-        <v>242</v>
+        <v>362</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A68" s="11"/>
       <c r="B68" s="7" t="s">
-        <v>347</v>
+        <v>306</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>245</v>
+        <v>218</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="H68" s="7"/>
       <c r="I68" s="7" t="s">
-        <v>246</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A69" s="11"/>
       <c r="B69" s="7" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="H69" s="7"/>
       <c r="I69" s="7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9" ht="114.75" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="127.5" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>350</v>
+        <v>307</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="E70" s="9" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="H70" s="9" t="s">
         <v>13</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>254</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="11"/>
       <c r="B71" s="7" t="s">
-        <v>351</v>
+        <v>308</v>
       </c>
       <c r="C71" s="12" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="7" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
     </row>
     <row r="72" spans="1:9" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>353</v>
+        <v>309</v>
       </c>
       <c r="C72" s="10" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="E72" s="9" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="H72" s="9"/>
       <c r="I72" s="9" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
